--- a/code/gpt_langchain/gpt_python/restaurants.xlsx
+++ b/code/gpt_langchain/gpt_python/restaurants.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10609"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/suntianran/Documents/GitHub/AI_project/code/gpt_langchain/gpt_python/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Horizon\Projects\Ongoing\AI_project\code\gpt_langchain\gpt_python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73BCCAF5-9379-7745-8C36-6A53B712D500}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0294B5A-A2E6-49B9-9557-8DA9F218635E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1060" yWindow="860" windowWidth="28100" windowHeight="17360" xr2:uid="{04E469E7-D3D3-F94F-85A7-F8C77A0574BD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{04E469E7-D3D3-F94F-85A7-F8C77A0574BD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
   <si>
     <t>Business Hours</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -100,13 +98,131 @@
   <si>
     <t>Recommend</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Building C, Unit 45ab, 1st Floor, No. 1000 Jianchuan Road, Zhuanqiao Town.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Niu Niu Sukiyaki Japanese Cuisine Buffet</t>
+  </si>
+  <si>
+    <t>Sukiyaki Beef, Assorted Sushi, Tempura</t>
+  </si>
+  <si>
+    <t>11:00-22:30</t>
+  </si>
+  <si>
+    <t>Braised Pork Belly, West Lake Fish in Vinegar Gravy, Stir-Fried Shrimp with Garlic</t>
+  </si>
+  <si>
+    <t>New Discovery Jiangsu-Zhejiang Cuisine</t>
+  </si>
+  <si>
+    <t>10:00-21:00</t>
+  </si>
+  <si>
+    <t>Whopper, Chicken Fries, Onion Rings</t>
+  </si>
+  <si>
+    <t>Burger King Fast Food</t>
+  </si>
+  <si>
+    <t>Building D, Unit 10, Lane 2000,Dong Chuan  Road, Units 5F-6F.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Building E, 2nd Floor, No. 800 South Hong Mei Road, City Center.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Building F, Unit 20, Lane 3000, SJTU Avenue.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tahar Xinjiang Cuisine</t>
+  </si>
+  <si>
+    <t>Lamb Skewers, Xinjiang-style Noodles, Big Plate Chicken</t>
+  </si>
+  <si>
+    <t>Building G, Unit 35, 3rd Floor, No. 1500 East Road, New District.</t>
+  </si>
+  <si>
+    <t>11:00-23:00</t>
+  </si>
+  <si>
+    <t>0:00-24:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12:00-16:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Xinjiang Kebab King</t>
+  </si>
+  <si>
+    <t>Grilled Lamb Skewers, Xinjiang-style Bread, Spicy Lamb Chops</t>
+  </si>
+  <si>
+    <t>Building H, Unit 5, Lane 4000, Dongchuan Road.</t>
+  </si>
+  <si>
+    <t>19:00-05:30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Xiao Yang Shengjian</t>
+  </si>
+  <si>
+    <t>Pan-Fried Pork Buns, Steamed Pork Dumplings, Scallion Pancakes</t>
+  </si>
+  <si>
+    <t>Building I, Unit 12, Lane 5000, Jiangchuan Road.</t>
+  </si>
+  <si>
+    <t>9:00-21:00</t>
+  </si>
+  <si>
+    <t>McDonald's Fast Food</t>
+  </si>
+  <si>
+    <t>Big Mac, Chicken Nuggets, Fries</t>
+  </si>
+  <si>
+    <t>Building J, Unit 22, Lane 6000, Hongmei South Road.</t>
+  </si>
+  <si>
+    <t>7:00-23:00</t>
+  </si>
+  <si>
+    <t>Pork and Chive Dumplings, Beef Dumplings, Spicy Soup Dumplings</t>
+  </si>
+  <si>
+    <t>Yuanji Dumplings</t>
+  </si>
+  <si>
+    <t>Building K, Unit 8, Lane 7000, Siyuan Road.</t>
+  </si>
+  <si>
+    <t>10:00-22:00</t>
+  </si>
+  <si>
+    <t>Caesar Salad, Spaghetti Carbonara, Grilled Chicken Breast</t>
+  </si>
+  <si>
+    <t>Sally's Western Cuisine</t>
+  </si>
+  <si>
+    <t>Building L, Unit 18, Lane 8000, East Road.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -121,6 +237,19 @@
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF24292F"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF24292F"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -145,8 +274,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -483,10 +618,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D279154-0730-8B48-AD54-B9ADA595164F}">
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="28.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="113.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="73.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -503,7 +644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -520,13 +661,16 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>9</v>
       </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
       <c r="D3">
         <v>4.4000000000000004</v>
       </c>
@@ -534,7 +678,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -549,6 +693,159 @@
       </c>
       <c r="E4" t="s">
         <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="2">
+        <v>4.7</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="2">
+        <v>3.2</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="2">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="2">
+        <v>2.8</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" s="2">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" s="2">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" s="2">
+        <v>3.4</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
